--- a/objects_created.xlsx
+++ b/objects_created.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Run ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Object Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Object Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -1998,6 +1986,566 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>e0961203-b5e8-42db-b7f0-b47763988ac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Create Service Profile for SP-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0add80ee-f376-42bc-8284-e77274d76887</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_511_MGMT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Create VPN Parcel 'Branch_VPN_511_MGMT' for in SP-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>b24050c6-d276-42a2-8f2e-489f5f42d41a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_511_MGMT.Branch_VPN_511_MGMT_Loop511</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_511_MGMT_Loop511' for in VPN 'Branch_VPN_511_MGMT' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/b24050c6-d276-42a2-8f2e-489f5f42d41a/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>bcca51c1-af8f-48a6-ac11-cf7cb76625a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Create VPN Parcel 'Branch_VPN_GNR' for in SP-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>96b250ad-3507-41df-8cdf-50575bf86555</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN710</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN710' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>51d8fdb9-c5aa-4832-9f5a-d0fbb616b347</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN714</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN714' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>50ae53f7-81ac-4698-b5eb-a8d2527532d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN720</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN720' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0ec86d62-fd79-4535-aaf9-309801c642f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN722</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN722' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>eac016db-49be-4f93-ac69-8bcc1ea4ccdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN725</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN725' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5aabcc86-e8a5-4e2a-9f58-7e3e16105095</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_GNR.Branch_VPN_GNR_VLAN726</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_GNR_VLAN726' for in VPN 'Branch_VPN_GNR' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/96b250ad-3507-41df-8cdf-50575bf86555/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>726a7758-a814-445e-b10c-bf8d091b4607</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_MS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Create VPN Parcel 'Branch_VPN_MS' for in SP-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>c149aad2-8651-4eb3-8868-3f12f67481a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_MS.Branch_VPN_MS_VLAN721</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_MS_VLAN721' for in VPN 'Branch_VPN_MS' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/c149aad2-8651-4eb3-8868-3f12f67481a9/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>93db60b0-a9e2-4378-a03c-f7da04d0e7c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_MS.Branch_VPN_MS_VLAN723</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_MS_VLAN723' for in VPN 'Branch_VPN_MS' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/c149aad2-8651-4eb3-8868-3f12f67481a9/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0ecf7a27-d3de-422d-9d8d-594efb6c9a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_MS.Branch_VPN_MS_VLAN728</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_MS_VLAN728' for in VPN 'Branch_VPN_MS' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/c149aad2-8651-4eb3-8868-3f12f67481a9/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>27fb73ef-e82d-4f4a-8af5-d680e5189725</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SP-MED_GNR_MS.Branch_VPN_MS.Branch_VPN_MS_VLAN729</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Create Interface Parcel 'Branch_VPN_MS_VLAN729' for in VPN 'Branch_VPN_MS' of Profile 'SP-MED_GNR_MS'</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/feature-profile/sdwan/service/0add80ee-f376-42bc-8284-e77274d76887/lan/vpn/c149aad2-8651-4eb3-8868-3f12f67481a9/interface/ethernet</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>b20364bd-8934-4a10-a098-f0d5f038cac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1772451103</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:31:43</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ConfigGroup</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CG-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Create Configuration Group for CG-MED_GNR_MS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>/dataservice/v1/config-group</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>8e06f7e2-825a-415f-a642-44cbcdadc6d3</t>
         </is>
       </c>
     </row>
